--- a/lawyer_forms/002_living_will_form--lawyer_forms.xlsx
+++ b/lawyer_forms/002_living_will_form--lawyer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,46 +515,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test_page</t>
+          <t>assets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What are your assets (e.g., properties, investments, insurance policies, etc.)?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>List all assets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>beneficiary_name</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>beneficiary_name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How would you like your assets to be distributed among beneficiaries?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>e.g., 25%, 50%, 75%</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>asset_value</t>
+          <t>beneficiary_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>asset_value</t>
+          <t>Please confirm the names of your beneficiaries.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,58 +597,62 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inheritance_share</t>
+          <t>executor_email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>inheritance_share</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your email address for executor contact?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>e.g., example@example.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>asset_type</t>
+          <t>executor_phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>asset_type</t>
+          <t>What is your phone number for executor contact?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>distribution_percentage</t>
+          <t>assets_owed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>distribution_percentage</t>
+          <t>How much do you owe to others (e.g., loans, debts, etc.)?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,23 +665,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>assets_owned</t>
+          <t>executor_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>assets_owned</t>
+          <t>Please confirm your executor's name.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,64 +693,64 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assets_left</t>
+          <t>distribution_percentage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assets_left</t>
+          <t>What is the percentage of assets you would like to leave for others?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assets_left_hint</t>
+          <t>assets_owned</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>assets_left_hint</t>
+          <t>Confirm the assets you would like to leave for your loved ones.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>executor_name</t>
+          <t>assets_owned_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>executor_name</t>
+          <t>Confirm the assets you would like to leave for your loved ones (2).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +762,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>executor_email</t>
+          <t>executor_email2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>executor_email</t>
+          <t>What is the email of your executor?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +785,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>executor_phone</t>
+          <t>executor_phone2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>executor_phone</t>
+          <t>What is the phone number of your executor?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +808,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>assets_owed</t>
+          <t>assets_left</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>assets_owed</t>
+          <t>Please confirm the assets you have left behind.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,12 +831,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assets_owed_hint</t>
+          <t>assets_left_hint</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>assets_owed_hint</t>
+          <t>Assets Left Hint</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +854,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>asset_value_hint</t>
+          <t>assets_owned_hint</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>asset_value_hint</t>
+          <t>Assets Owned Hint</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>distribution_percentage_hint</t>
+          <t>assets_owed_hint</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>distribution_percentage_hint</t>
+          <t>Assets Owed Hint</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +900,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>assets_owned_hint</t>
+          <t>executor_name_hint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>assets_owned_hint</t>
+          <t>Executor Name Hint</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +923,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assets_left_hint</t>
+          <t>executor_phone_hint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>assets_left_hint</t>
+          <t>Executor Phone Hint</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +946,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>executor_name_hint</t>
+          <t>executor_email_hint</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>executor_name_hint</t>
+          <t>Executor Email Hint</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +969,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>executor_email_hint</t>
+          <t>assets_owed_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>executor_email_hint</t>
+          <t>Assets Owed</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +992,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>executor_phone_hint</t>
+          <t>assets_owed_hint_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>executor_phone_hint</t>
+          <t>Assets Owed Hint 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,17 +1010,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>assets_owed_hint</t>
+          <t>assets_owned_2_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>assets_owed_hint</t>
+          <t>Assets Owned 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,62 +1038,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>assets_owed_hint</t>
+          <t>assets_owned_2_hint</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>assets_owed_hint</t>
+          <t>Assets Owned 2 Hint</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assets_owned_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>assets_owned_2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>assets_owned_2_hint</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>assets_owned_2_hint</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1064,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +1092,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>asset_type_choices</t>
+          <t>assets_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1109,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>asset_type_choices</t>
+          <t>assets_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1126,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>asset_type_choices</t>
+          <t>assets_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,51 +1143,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>distribution_percentage_choices</t>
+          <t>distribution_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>distribution_percentage_choices</t>
+          <t>distribution_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>distribution_percentage_choices</t>
+          <t>distribution_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1324,6 +1290,40 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Asset I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>assets_owned_2_2_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>assets_owned_2_2_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Option B</t>
         </is>
       </c>
     </row>
